--- a/sharedata/excel/J-技能表(SkillData).xlsx
+++ b/sharedata/excel/J-技能表(SkillData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
   <si>
     <t>组id+2位等级</t>
   </si>
@@ -70,6 +70,12 @@
     <t>解锁等级</t>
   </si>
   <si>
+    <t>施法特效</t>
+  </si>
+  <si>
+    <t>特效延迟</t>
+  </si>
+  <si>
     <t>SkillData</t>
   </si>
   <si>
@@ -100,6 +106,12 @@
     <t>unlock_lv</t>
   </si>
   <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>effect_delay</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -112,6 +124,12 @@
     <t>lang</t>
   </si>
   <si>
+    <t>string_list</t>
+  </si>
+  <si>
+    <t>float_list</t>
+  </si>
+  <si>
     <t>逻辑检查</t>
   </si>
   <si>
@@ -121,6 +139,12 @@
     <t>ref(IconData)</t>
   </si>
   <si>
+    <t>ref(EffectData)</t>
+  </si>
+  <si>
+    <t>size(effect)</t>
+  </si>
+  <si>
     <t>临时英雄_1_技能1_lv1</t>
   </si>
   <si>
@@ -133,6 +157,9 @@
     <t>$Lang$技能.200101.1级描述</t>
   </si>
   <si>
+    <t>临时英雄主动技能</t>
+  </si>
+  <si>
     <t>临时英雄_1_技能1_lv2</t>
   </si>
   <si>
@@ -169,6 +196,9 @@
     <t>$Lang$技能.200102.1级描述</t>
   </si>
   <si>
+    <t>临时英雄被动技能</t>
+  </si>
+  <si>
     <t>临时英雄_1_技能2_lv2</t>
   </si>
   <si>
@@ -191,6 +221,51 @@
   </si>
   <si>
     <t>$Lang$技能.200102.5级描述</t>
+  </si>
+  <si>
+    <t>临时专属技能_lv1</t>
+  </si>
+  <si>
+    <t>临时专属技能</t>
+  </si>
+  <si>
+    <t>临时技能占位；仅用于专属装备配置引用，战斗效果尚未接入</t>
+  </si>
+  <si>
+    <t>临时神器技能_lv1</t>
+  </si>
+  <si>
+    <t>临时神器技能</t>
+  </si>
+  <si>
+    <t>临时神器技能1级占位；战斗效果尚未接入</t>
+  </si>
+  <si>
+    <t>临时神器技能_lv2</t>
+  </si>
+  <si>
+    <t>临时神器技能2级占位；战斗效果尚未接入</t>
+  </si>
+  <si>
+    <t>临时小兵近战普攻_lv1</t>
+  </si>
+  <si>
+    <t>临时小兵近战普攻</t>
+  </si>
+  <si>
+    <t>临时普通攻击元数据占位；攻击结算和播放配置尚未接入</t>
+  </si>
+  <si>
+    <t>临时小兵远程普攻_lv1</t>
+  </si>
+  <si>
+    <t>临时小兵远程普攻</t>
+  </si>
+  <si>
+    <t>临时英雄普攻_lv1</t>
+  </si>
+  <si>
+    <t>临时英雄普攻</t>
   </si>
 </sst>
 </file>
@@ -203,7 +278,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
@@ -223,6 +298,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
@@ -380,11 +462,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -709,157 +789,159 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,22 +958,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="52">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -942,6 +1018,8 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="常规 3" xfId="50"/>
+    <cellStyle name="常规 2" xfId="51"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1361,38 +1439,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.11111111111111" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.6666666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="11.8888888888889" style="3" customWidth="1"/>
     <col min="3" max="3" width="13.6666666666667" style="3" customWidth="1"/>
-    <col min="4" max="5" width="18.5555555555556" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.7777777777778" style="3" customWidth="1"/>
-    <col min="7" max="7" width="24.6666666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.8888888888889" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.8888888888889" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.3333333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22" style="3" customWidth="1"/>
+    <col min="7" max="7" width="49.8888888888889" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15" style="3" customWidth="1"/>
+    <col min="9" max="9" width="7.88888888888889" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.1111111111111" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.1111111111111" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6"/>
+      <c r="D1" s="5"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" s="4"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1423,514 +1506,534 @@
       <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:10">
-      <c r="A4" s="7" t="s">
+      <c r="K3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="L3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:12">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="D4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:12">
+      <c r="A5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:12">
+      <c r="A6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="H6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="7">
+        <v>20010101</v>
+      </c>
+      <c r="C7" s="7">
+        <v>200101</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" s="7">
+        <v>20010102</v>
+      </c>
+      <c r="C8" s="7">
+        <v>200101</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7">
         <v>20</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
-      <c r="A5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
-      <c r="A6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="H6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B7" s="8">
-        <v>20010101</v>
-      </c>
-      <c r="C7" s="8">
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="7">
+        <v>20010103</v>
+      </c>
+      <c r="C9" s="7">
         <v>200101</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="str" s="9">
-        <v>临时英雄主动技能</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="D9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="7">
+        <v>3</v>
+      </c>
+      <c r="J9" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10" s="7">
+        <v>20010104</v>
+      </c>
+      <c r="C10" s="7">
+        <v>200101</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="7">
+        <v>4</v>
+      </c>
+      <c r="J10" s="7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="7">
+        <v>20010105</v>
+      </c>
+      <c r="C11" s="7">
+        <v>200101</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="7">
+        <v>5</v>
+      </c>
+      <c r="J11" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="7">
+        <v>20010201</v>
+      </c>
+      <c r="C12" s="7">
+        <v>200102</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="7">
         <v>1</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J12" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B8" s="8">
-        <v>20010102</v>
-      </c>
-      <c r="C8" s="8">
-        <v>200101</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="str" s="9">
-        <v>临时英雄主动技能</v>
-      </c>
-      <c r="I8" s="8">
+    <row r="13" spans="1:12">
+      <c r="B13" s="7">
+        <v>20010202</v>
+      </c>
+      <c r="C13" s="7">
+        <v>200102</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="7">
         <v>2</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J13" s="7">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B9" s="8">
-        <v>20010103</v>
-      </c>
-      <c r="C9" s="8">
-        <v>200101</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" t="str" s="9">
-        <v>临时英雄主动技能</v>
-      </c>
-      <c r="I9" s="8">
+    <row r="14" spans="1:12">
+      <c r="B14" s="7">
+        <v>20010203</v>
+      </c>
+      <c r="C14" s="7">
+        <v>200102</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="7">
         <v>3</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J14" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B10" s="8">
-        <v>20010104</v>
-      </c>
-      <c r="C10" s="8">
-        <v>200101</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="str" s="9">
-        <v>临时英雄主动技能</v>
-      </c>
-      <c r="I10" s="8">
+    <row r="15" spans="1:12">
+      <c r="B15" s="7">
+        <v>20010204</v>
+      </c>
+      <c r="C15" s="7">
+        <v>200102</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="7">
         <v>4</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J15" s="7">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B11" s="8">
-        <v>20010105</v>
-      </c>
-      <c r="C11" s="8">
-        <v>200101</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="str" s="9">
-        <v>临时英雄主动技能</v>
-      </c>
-      <c r="I11" s="8">
+    <row r="16" spans="1:12">
+      <c r="B16" s="7">
+        <v>20010205</v>
+      </c>
+      <c r="C16" s="7">
+        <v>200102</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="7">
         <v>5</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J16" s="7">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B12" s="8">
-        <v>20010201</v>
-      </c>
-      <c r="C12" s="8">
-        <v>200102</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" t="str" s="9">
-        <v>临时英雄被动技能</v>
-      </c>
-      <c r="I12" s="8">
+    <row r="17" spans="2:10">
+      <c r="B17" s="7">
+        <v>20010301</v>
+      </c>
+      <c r="C17" s="7">
+        <v>200103</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="7">
         <v>1</v>
       </c>
-      <c r="J12" s="8">
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="7">
+        <v>20010401</v>
+      </c>
+      <c r="C18" s="7">
+        <v>200104</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B13" s="8">
-        <v>20010202</v>
-      </c>
-      <c r="C13" s="8">
-        <v>200102</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" t="str" s="9">
-        <v>临时英雄被动技能</v>
-      </c>
-      <c r="I13" s="8">
+    <row r="19" spans="2:10">
+      <c r="B19" s="7">
+        <v>20010402</v>
+      </c>
+      <c r="C19" s="7">
+        <v>200104</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="7">
         <v>2</v>
       </c>
-      <c r="J13" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B14" s="8">
-        <v>20010203</v>
-      </c>
-      <c r="C14" s="8">
-        <v>200102</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" t="str" s="9">
-        <v>临时英雄被动技能</v>
-      </c>
-      <c r="I14" s="8">
-        <v>3</v>
-      </c>
-      <c r="J14" s="8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B15" s="8">
-        <v>20010204</v>
-      </c>
-      <c r="C15" s="8">
-        <v>200102</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" t="str" s="9">
-        <v>临时英雄被动技能</v>
-      </c>
-      <c r="I15" s="8">
-        <v>4</v>
-      </c>
-      <c r="J15" s="8">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="33.0" customHeight="1">
-      <c r="B16" s="8">
-        <v>20010205</v>
-      </c>
-      <c r="C16" s="8">
-        <v>200102</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" t="str" s="9">
-        <v>临时英雄被动技能</v>
-      </c>
-      <c r="I16" s="8">
-        <v>5</v>
-      </c>
-      <c r="J16" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" ht="49.5" customHeight="1">
-      <c r="B17" t="n" s="8">
-        <v>20010301</v>
-      </c>
-      <c r="C17" t="n" s="8">
-        <v>200103</v>
-      </c>
-      <c r="D17" t="str" s="9">
-        <v>临时专属技能_lv1</v>
-      </c>
-      <c r="E17" t="str" s="9">
-        <v>临时专属技能</v>
-      </c>
-      <c r="F17" t="str" s="8">
-        <v>临时专属技能</v>
-      </c>
-      <c r="G17" t="str" s="9">
-        <v>临时技能占位；仅用于专属装备配置引用，战斗效果尚未接入</v>
-      </c>
-      <c r="H17" t="str" s="9">
-        <v>临时专属技能</v>
-      </c>
-      <c r="I17" t="n" s="8">
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="7">
+        <v>10010101</v>
+      </c>
+      <c r="C20" s="7">
+        <v>100101</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="7">
         <v>1</v>
       </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" ht="33.0" customHeight="1">
-      <c r="B18" t="n" s="8">
-        <v>20010401</v>
-      </c>
-      <c r="C18" t="n" s="8">
-        <v>200104</v>
-      </c>
-      <c r="D18" t="str" s="9">
-        <v>临时神器技能_lv1</v>
-      </c>
-      <c r="E18" t="str" s="9">
-        <v>临时神器技能</v>
-      </c>
-      <c r="F18" t="str" s="8">
-        <v>临时神器技能</v>
-      </c>
-      <c r="G18" t="str" s="9">
-        <v>临时神器技能1级占位；战斗效果尚未接入</v>
-      </c>
-      <c r="H18" t="str" s="9">
-        <v>临时神器技能</v>
-      </c>
-      <c r="I18" t="n" s="8">
+      <c r="J20" s="7">
         <v>1</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
-      <c r="B19" t="n" s="8">
-        <v>20010402</v>
-      </c>
-      <c r="C19" t="n" s="8">
-        <v>200104</v>
-      </c>
-      <c r="D19" t="str" s="9">
-        <v>临时神器技能_lv2</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" t="str" s="8">
-        <v>临时神器技能</v>
-      </c>
-      <c r="G19" t="str" s="9">
-        <v>临时神器技能2级占位；战斗效果尚未接入</v>
-      </c>
-      <c r="H19" t="str" s="9">
-        <v>临时神器技能</v>
-      </c>
-      <c r="I19" t="n" s="8">
-        <v>2</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" ht="49.5" customHeight="1">
-      <c r="B20" t="n" s="8">
-        <v>10010101</v>
-      </c>
-      <c r="C20" t="n" s="8">
-        <v>100101</v>
-      </c>
-      <c r="D20" t="str" s="9">
-        <v>临时小兵近战普攻_lv1</v>
-      </c>
-      <c r="E20" t="str" s="9">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="F20" t="str" s="8">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="G20" t="str" s="9">
-        <v>临时普通攻击元数据占位；攻击结算和播放配置尚未接入</v>
-      </c>
-      <c r="H20" t="str" s="9">
-        <v>临时小兵近战普攻</v>
-      </c>
-      <c r="I20" t="n" s="8">
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="7">
+        <v>10010201</v>
+      </c>
+      <c r="C21" s="7">
+        <v>100102</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="7">
         <v>1</v>
       </c>
-      <c r="J20" t="n" s="8">
+      <c r="J21" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="B21" t="n" s="8">
-        <v>10010201</v>
-      </c>
-      <c r="C21" t="n" s="8">
-        <v>100102</v>
-      </c>
-      <c r="D21" t="str" s="9">
-        <v>临时小兵远程普攻_lv1</v>
-      </c>
-      <c r="E21" t="str" s="9">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="F21" t="str" s="8">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="G21" t="str" s="9">
-        <v>临时普通攻击元数据占位；攻击结算和播放配置尚未接入</v>
-      </c>
-      <c r="H21" t="str" s="9">
-        <v>临时小兵远程普攻</v>
-      </c>
-      <c r="I21" t="n" s="8">
+    <row r="22" spans="2:10">
+      <c r="B22" s="7">
+        <v>20010501</v>
+      </c>
+      <c r="C22" s="7">
+        <v>200105</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="7">
         <v>1</v>
       </c>
-      <c r="J21" t="n" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
-      <c r="B22" t="n" s="8">
-        <v>20010501</v>
-      </c>
-      <c r="C22" t="n" s="8">
-        <v>200105</v>
-      </c>
-      <c r="D22" t="str" s="9">
-        <v>临时英雄普攻_lv1</v>
-      </c>
-      <c r="E22" t="str" s="9">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="F22" t="str" s="8">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="G22" t="str" s="9">
-        <v>临时普通攻击元数据占位；攻击结算和播放配置尚未接入</v>
-      </c>
-      <c r="H22" t="str" s="9">
-        <v>临时英雄普攻</v>
-      </c>
-      <c r="I22" t="n" s="8">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n" s="8">
+      <c r="J22" s="7">
         <v>1</v>
       </c>
     </row>
